--- a/DB2_26Feb26_intact/pac.xlsx
+++ b/DB2_26Feb26_intact/pac.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://proteinsolution-my.sharepoint.com/personal/drobles_pronokal_com/Documents/Escritorio/v4 2024_03_2025/entregable/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{DF0EAC5F-AF94-4837-9F56-03A6D3088AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E53B4401-003A-47EE-AFE7-E9375D478851}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4506"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19420" windowHeight="11020"/>
   </bookViews>
   <sheets>
     <sheet name="pac_cientifico" sheetId="1" r:id="rId1"/>
@@ -4998,7 +4992,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -5033,12 +5027,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -5050,6 +5041,9 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5065,22 +5059,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:M1626" totalsRowShown="0">
-  <autoFilter ref="A1:M1626" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:M1626" totalsRowShown="0">
+  <autoFilter ref="A1:M1626"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{7C224378-8F5F-47CF-92DE-873FF09EC01D}" name="Id Paciente" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Fecha de creación"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Sexo" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{5673CF71-155F-460F-ABC0-7DFEE8B9A0F6}" name="Compra Online" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Patient Collective"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="NAV Company Lower"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Fecha de nacimiento"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="GDPR-4"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Fecha GDPR-4"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="GDPR-10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Fecha GDPR-10"/>
-    <tableColumn id="2" xr3:uid="{2E5E3CFE-BE01-4091-8729-9E6F3C10FB27}" name="genomics_available" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{0CE2C0B1-8005-49C2-8AB8-87B485ACA289}" name="Muestra" dataDxfId="1"/>
+    <tableColumn id="1" name="Id Paciente" dataDxfId="4"/>
+    <tableColumn id="5" name="Fecha de creación"/>
+    <tableColumn id="6" name="Sexo" dataDxfId="3"/>
+    <tableColumn id="18" name="Compra Online" dataDxfId="2"/>
+    <tableColumn id="8" name="Patient Collective"/>
+    <tableColumn id="9" name="NAV Company Lower"/>
+    <tableColumn id="10" name="Fecha de nacimiento"/>
+    <tableColumn id="13" name="GDPR-4"/>
+    <tableColumn id="14" name="Fecha GDPR-4"/>
+    <tableColumn id="15" name="GDPR-10"/>
+    <tableColumn id="16" name="Fecha GDPR-10"/>
+    <tableColumn id="2" name="genomics_available" dataDxfId="1"/>
+    <tableColumn id="19" name="Muestra" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5129,7 +5123,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5181,7 +5175,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -5395,17 +5389,17 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="dataSheet"/>
   <dimension ref="A1:M1626"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28" style="4" customWidth="1"/>
     <col min="2" max="2" width="28" style="2" customWidth="1"/>
@@ -52681,20 +52675,20 @@
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" errorTitle="Valor de lista" error="Compra Genomics debe estar seleccionado en la lista desplegable." promptTitle="Conjunto de opciones" prompt="Seleccione un valor de la lista desplegable." sqref="L2:M1626" xr:uid="{25BB0301-C2F0-48FA-9AD3-5B611B3F96D0}"/>
-    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha de creación debe estar en el formato de fecha y hora correcto." promptTitle="Fecha y hora" prompt=" " sqref="B2:C1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation allowBlank="1" errorTitle="Valor de lista" error="Compra Genomics debe estar seleccionado en la lista desplegable." promptTitle="Conjunto de opciones" prompt="Seleccione un valor de la lista desplegable." sqref="L2:M1626"/>
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha de creación debe estar en el formato de fecha y hora correcto." promptTitle="Fecha y hora" prompt=" " sqref="B2:C1048576">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Longitud excedida" error="Este valor debe tener 4000 caracteres o menos." promptTitle="Texto" prompt="Longitud máxima: 4000 caracteres." sqref="G1627:G1048576 F2:F1626" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Longitud excedida" error="Este valor debe tener 4000 caracteres o menos." promptTitle="Texto" prompt="Longitud máxima: 4000 caracteres." sqref="G1627:G1048576 F2:F1626">
       <formula1>4000</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha de nacimiento debe estar en el formato de fecha correcto." promptTitle="Fecha" prompt=" " sqref="G2:G1626" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha de nacimiento debe estar en el formato de fecha correcto." promptTitle="Fecha" prompt=" " sqref="G2:G1626">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha autorización uso datos estudios médicos debe estar en el formato de fecha y hora correcto." promptTitle="Fecha y hora" prompt=" " sqref="J1627:J1048576 I2:I1626" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha autorización uso datos estudios médicos debe estar en el formato de fecha y hora correcto." promptTitle="Fecha y hora" prompt=" " sqref="J1627:J1048576 I2:I1626">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha autorización datos de salud y genéticos debe estar en el formato de fecha y hora correcto." promptTitle="Fecha y hora" prompt=" " sqref="L1627:L1048576 K2:K1626" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Fecha autorización datos de salud y genéticos debe estar en el formato de fecha y hora correcto." promptTitle="Fecha y hora" prompt=" " sqref="L1627:L1048576 K2:K1626">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
@@ -52702,7 +52696,7 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-  <extLst>
+  <extLst xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor de lista" error="Compra Genomics debe estar seleccionado en la lista desplegable." promptTitle="Conjunto de opciones" prompt="Seleccione un valor de la lista desplegable." xr:uid="{00000000-0002-0000-0000-00000E000000}">
@@ -52754,10 +52748,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="hiddenDataSheet"/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
